--- a/other/covid_19_vaccine_intake_consent_form.xlsx
+++ b/other/covid_19_vaccine_intake_consent_form.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'pfizer',_'value':_'pfizer'}</t>
+          <t>pfizer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Pfizer', 'value': 'pfizer'}</t>
+          <t>Pfizer</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'moderna',_'value':_'moderna'}</t>
+          <t>moderna</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Moderna', 'value': 'moderna'}</t>
+          <t>Moderna</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'high_blood_pressure',_'value':_'high-blood-pressure'}</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'High Blood Pressure', 'value': 'high-blood-pressure'}</t>
+          <t>High Blood Pressure</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'diabetes',_'value':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Diabetes', 'value': 'diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'asthma',_'value':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Asthma', 'value': 'asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
